--- a/informes_data/Segunda FEB/2026-27/Regular_Season/individual/NP_play_by_play_2536116_LIGAREGULARA_PROCESSED.xlsx
+++ b/informes_data/Segunda FEB/2026-27/Regular_Season/individual/NP_play_by_play_2536116_LIGAREGULARA_PROCESSED.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y29"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1044,7 +1044,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. RAMÍREZ SÁNCHEZ</t>
+          <t>R. REID</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1056,58 +1056,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6075</v>
+        <v>-0.205</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6075</v>
+        <v>-0.905</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6075</v>
+        <v>-0.7936</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>-1.508</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6075</v>
+        <v>0.7144</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6075</v>
+        <v>-0.7245</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>-1.2995</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6075</v>
+        <v>0.575</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>-0.06909999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>-0.2085</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>0.1394</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.7799</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>0.7799</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-0.1914</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>-0.1805</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>-0.0109</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. REID</t>
+          <t>T. VAN BRANDWIJK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1139,67 +1139,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.205</v>
+        <v>-0.3723</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.905</v>
+        <v>-0.195</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7</v>
+        <v>-0.1772</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.7936</v>
+        <v>0.4471</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.508</v>
+        <v>0.1344</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7144</v>
+        <v>0.3127</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.7245</v>
+        <v>0.0405</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.2995</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.575</v>
+        <v>0.0405</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.06909999999999999</v>
+        <v>0.4066</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2085</v>
+        <v>0.1344</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1394</v>
+        <v>0.2722</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7799</v>
+        <v>0.195</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7799</v>
+        <v>0.195</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1914</v>
+        <v>-0.7358</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1805</v>
+        <v>-0.2355</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0109</v>
+        <v>-0.5003</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.2786</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.2786</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T. VAN BRANDWIJK</t>
+          <t>D. RAMIREZ SANCHEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1222,67 +1222,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.3723</v>
+        <v>-0.8491</v>
       </c>
       <c r="E10" t="n">
+        <v>-1.8727</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.0235</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-4.4957</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-2.1885</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-2.3072</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-2.9325</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-1.0204</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-1.912</v>
+      </c>
+      <c r="M10" t="n">
+        <v>-1.5632</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-1.1681</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-0.3951</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.9499</v>
+      </c>
+      <c r="Q10" t="n">
         <v>-0.195</v>
       </c>
-      <c r="F10" t="n">
-        <v>-0.1772</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.4471</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.1344</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.3127</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.0405</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.0405</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0.4066</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0.1344</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0.2722</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0.195</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
-        <v>0.195</v>
+        <v>2.1448</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7358</v>
+        <v>0.251</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2355</v>
+        <v>-0.1909</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5003</v>
+        <v>0.4419</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2786</v>
+        <v>1.4457</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.4457</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2786</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. RAMIREZ SANCHEZ</t>
+          <t>A. MARIN ORTEGA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1471,64 +1471,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.4567</v>
+        <v>-3.1924</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.4802</v>
+        <v>-3.2126</v>
       </c>
       <c r="F13" t="n">
-        <v>1.0235</v>
+        <v>0.0201</v>
       </c>
       <c r="G13" t="n">
-        <v>-5.1032</v>
+        <v>-3.7596</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.1885</v>
+        <v>-0.7978</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.9147</v>
+        <v>-2.9618</v>
       </c>
       <c r="J13" t="n">
-        <v>-3.54</v>
+        <v>-2.341</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.0204</v>
+        <v>-0.3155</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.5196</v>
+        <v>-2.0255</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.5632</v>
+        <v>-1.4186</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.1681</v>
+        <v>-0.4824</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.3951</v>
+        <v>-0.9363</v>
       </c>
       <c r="P13" t="n">
-        <v>1.9499</v>
+        <v>0.195</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.195</v>
+        <v>-1.1699</v>
       </c>
       <c r="R13" t="n">
-        <v>2.1448</v>
+        <v>1.3649</v>
       </c>
       <c r="S13" t="n">
-        <v>0.251</v>
+        <v>0.0936</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1909</v>
+        <v>0.0198</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4419</v>
+        <v>0.0738</v>
       </c>
       <c r="V13" t="n">
-        <v>1.4457</v>
+        <v>0.2786</v>
       </c>
       <c r="W13" t="n">
-        <v>1.4457</v>
+        <v>0.2786</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1542,7 +1542,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. MARIN ORTEGA</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1554,157 +1554,157 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.1924</v>
+        <v>18.0372</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.2126</v>
+        <v>10.2657</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0201</v>
+        <v>7.771500000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>-3.7596</v>
+        <v>3.319400000000003</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.7978</v>
+        <v>-0.0171</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.9618</v>
+        <v>3.336699999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.341</v>
+        <v>12.4564</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.3155</v>
+        <v>5.168299999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>-2.0255</v>
+        <v>7.287900000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.4186</v>
+        <v>-9.136900000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.4824</v>
+        <v>-5.185700000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.9363</v>
+        <v>-3.9512</v>
       </c>
       <c r="P14" t="n">
-        <v>0.195</v>
+        <v>6.824599999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1699</v>
+        <v>-9.7492</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3649</v>
+        <v>16.5737</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0936</v>
+        <v>2.3358</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0198</v>
+        <v>-0.2799</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0738</v>
+        <v>2.615799999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>0.2786</v>
+        <v>5.557300000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>0.2786</v>
+        <v>7.8387</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>play_by_play_2536116_LIGAREGULARA_PROCESSED.xlsx</t>
-        </is>
-      </c>
+        <v>-2.2813</v>
+      </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>P. MONES RIERA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CB ALGECIRAS</t>
+          <t>IREN BCBADAJOZ</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>18.0371</v>
+        <v>3.7636</v>
       </c>
       <c r="E15" t="n">
-        <v>10.2657</v>
+        <v>3.8115</v>
       </c>
       <c r="F15" t="n">
-        <v>7.771500000000001</v>
+        <v>-0.0479</v>
       </c>
       <c r="G15" t="n">
-        <v>3.319400000000002</v>
+        <v>1.3581</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.0171</v>
+        <v>0.078</v>
       </c>
       <c r="I15" t="n">
-        <v>3.336699999999999</v>
+        <v>1.28</v>
       </c>
       <c r="J15" t="n">
-        <v>12.4564</v>
+        <v>3.5968</v>
       </c>
       <c r="K15" t="n">
-        <v>5.1683</v>
+        <v>1.6527</v>
       </c>
       <c r="L15" t="n">
-        <v>7.2878</v>
+        <v>1.9441</v>
       </c>
       <c r="M15" t="n">
-        <v>-9.136900000000001</v>
+        <v>-2.2387</v>
       </c>
       <c r="N15" t="n">
-        <v>-5.185700000000001</v>
+        <v>-1.5746</v>
       </c>
       <c r="O15" t="n">
-        <v>-3.9512</v>
+        <v>-0.664</v>
       </c>
       <c r="P15" t="n">
-        <v>6.8246</v>
+        <v>0.7799</v>
       </c>
       <c r="Q15" t="n">
-        <v>-9.7492</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>16.5737</v>
+        <v>0.7799</v>
       </c>
       <c r="S15" t="n">
-        <v>2.3358</v>
+        <v>0.2997</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2799</v>
+        <v>0.2148</v>
       </c>
       <c r="U15" t="n">
-        <v>2.6158</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>5.5573</v>
+        <v>1.3259</v>
       </c>
       <c r="W15" t="n">
-        <v>7.8387</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.2813</v>
-      </c>
-      <c r="Y15" t="inlineStr"/>
+        <v>1.3259</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2536116_LIGAREGULARA_PROCESSED.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. MONES RIERA</t>
+          <t>J. KELLIER</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1716,67 +1716,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.7636</v>
+        <v>1.6831</v>
       </c>
       <c r="E16" t="n">
-        <v>3.8115</v>
+        <v>1.3583</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0479</v>
+        <v>0.3248</v>
       </c>
       <c r="G16" t="n">
-        <v>1.3581</v>
+        <v>0.1823</v>
       </c>
       <c r="H16" t="n">
-        <v>0.078</v>
+        <v>0.2779</v>
       </c>
       <c r="I16" t="n">
-        <v>1.28</v>
+        <v>-0.0956</v>
       </c>
       <c r="J16" t="n">
-        <v>3.5968</v>
+        <v>0.7185</v>
       </c>
       <c r="K16" t="n">
-        <v>1.6527</v>
+        <v>0.1435</v>
       </c>
       <c r="L16" t="n">
-        <v>1.9441</v>
+        <v>0.575</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.2387</v>
+        <v>-0.5363</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.5746</v>
+        <v>0.1344</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.664</v>
+        <v>-0.6706</v>
       </c>
       <c r="P16" t="n">
-        <v>0.7799</v>
+        <v>0.585</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.7799</v>
+        <v>0.585</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2997</v>
+        <v>0.6373</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2148</v>
+        <v>0.3612</v>
       </c>
       <c r="U16" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.2761</v>
       </c>
       <c r="V16" t="n">
-        <v>1.3259</v>
+        <v>0.2786</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.2786</v>
       </c>
       <c r="X16" t="n">
-        <v>1.3259</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. KELLIER</t>
+          <t>N. RAKOCEVIC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1799,67 +1799,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.6831</v>
+        <v>1.2644</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3583</v>
+        <v>2.4866</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3248</v>
+        <v>-1.2222</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1823</v>
+        <v>2.8182</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2779</v>
+        <v>2.8309</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0956</v>
+        <v>-0.0127</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7185</v>
+        <v>4.2304</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1435</v>
+        <v>3.4529</v>
       </c>
       <c r="L17" t="n">
-        <v>0.575</v>
+        <v>0.7775</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5363</v>
+        <v>-1.4122</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1344</v>
+        <v>-0.6219</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6706</v>
+        <v>-0.7903</v>
       </c>
       <c r="P17" t="n">
-        <v>0.585</v>
+        <v>-1.5599</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-2.9248</v>
       </c>
       <c r="R17" t="n">
-        <v>0.585</v>
+        <v>1.3649</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6373</v>
+        <v>-0.4819</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3612</v>
+        <v>-0.9276</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2761</v>
+        <v>0.4457</v>
       </c>
       <c r="V17" t="n">
-        <v>0.2786</v>
+        <v>0.488</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2786</v>
+        <v>2.1086</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.6206</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>N. RAKOCEVIC</t>
+          <t>A. MERLO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1882,67 +1882,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.2644</v>
+        <v>-0.4164</v>
       </c>
       <c r="E18" t="n">
-        <v>2.4866</v>
+        <v>-0.6713</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.2222</v>
+        <v>0.2549</v>
       </c>
       <c r="G18" t="n">
-        <v>2.8182</v>
+        <v>1.6941</v>
       </c>
       <c r="H18" t="n">
-        <v>2.8309</v>
+        <v>-0.3263</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0127</v>
+        <v>2.0204</v>
       </c>
       <c r="J18" t="n">
-        <v>4.2304</v>
+        <v>0.6726</v>
       </c>
       <c r="K18" t="n">
-        <v>3.4529</v>
+        <v>-0.664</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7775</v>
+        <v>1.3365</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.4122</v>
+        <v>1.0215</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6219</v>
+        <v>0.3377</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.7903</v>
+        <v>0.6838</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.5599</v>
+        <v>0.195</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.9248</v>
+        <v>-0.9749</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3649</v>
+        <v>1.1699</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4819</v>
+        <v>-0.4754</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9276</v>
+        <v>-0.369</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4457</v>
+        <v>-0.1064</v>
       </c>
       <c r="V18" t="n">
-        <v>0.488</v>
+        <v>-1.8301</v>
       </c>
       <c r="W18" t="n">
-        <v>2.1086</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.6206</v>
+        <v>-1.8301</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Á. MERLO</t>
+          <t>A. DEL CERRO MARTIN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1965,67 +1965,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.215</v>
+        <v>-1.3701</v>
       </c>
       <c r="E19" t="n">
-        <v>1.215</v>
+        <v>-0.4616</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>-0.9085</v>
       </c>
       <c r="G19" t="n">
-        <v>1.215</v>
+        <v>-0.0361</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>0.5535</v>
       </c>
       <c r="I19" t="n">
-        <v>1.215</v>
+        <v>-0.5896</v>
       </c>
       <c r="J19" t="n">
-        <v>1.215</v>
+        <v>0.0936</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>0.6931</v>
       </c>
       <c r="L19" t="n">
-        <v>1.215</v>
+        <v>-0.5995</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>-0.1297</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>-0.1395</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.585</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>0.585</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>-0.2454</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>-0.2237</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>-0.0217</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-1.6735</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.3315</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.3421</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. OSÉS BERNALDÉZ</t>
+          <t>A. DIAZ FERREIRA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2048,58 +2048,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6075</v>
+        <v>-1.4162</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6075</v>
+        <v>-0.6254999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>-0.7906</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6075</v>
+        <v>-0.5662</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>-0.205</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6075</v>
+        <v>-0.3612</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6075</v>
+        <v>0.0405</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6075</v>
+        <v>0.0405</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>-0.6067</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>-0.205</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>-0.4017</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-0.9749</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.9749</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>0.3089</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>-0.1839</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2119,7 +2119,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. DEL CERRO MARTIN</t>
+          <t>L. BRYAN JR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2131,67 +2131,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.3701</v>
+        <v>-1.7129</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.4616</v>
+        <v>-0.4782</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9085</v>
+        <v>-1.2347</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0361</v>
+        <v>-1.5977</v>
       </c>
       <c r="H21" t="n">
-        <v>0.5535</v>
+        <v>-0.1156</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5896</v>
+        <v>-1.4821</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0936</v>
+        <v>0.6261</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6931</v>
+        <v>0.5046</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5995</v>
+        <v>0.1215</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1297</v>
+        <v>-2.2238</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1395</v>
+        <v>-0.6202</v>
       </c>
       <c r="O21" t="n">
-        <v>0.009900000000000001</v>
+        <v>-1.6036</v>
       </c>
       <c r="P21" t="n">
-        <v>0.585</v>
+        <v>0.195</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.9749</v>
       </c>
       <c r="R21" t="n">
-        <v>0.585</v>
+        <v>1.1699</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2454</v>
+        <v>0.6475</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2237</v>
+        <v>-0.1294</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0217</v>
+        <v>0.7768</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.6735</v>
+        <v>-0.9577</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.3315</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.3421</v>
+        <v>-0.9577</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. DIAZ FERREIRA</t>
+          <t>U. RAZAQUE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2214,67 +2214,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.4162</v>
+        <v>-1.9784</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.6254999999999999</v>
+        <v>-1.9102</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7906</v>
+        <v>-0.0682</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.5662</v>
+        <v>-0.3791</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.205</v>
+        <v>0.1116</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.3612</v>
+        <v>-0.4907</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0405</v>
+        <v>0.7692</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>1.2797</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0405</v>
+        <v>-0.5105</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.6067</v>
+        <v>-1.1483</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.205</v>
+        <v>-1.1681</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.4017</v>
+        <v>0.0198</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.9749</v>
+        <v>-0.585</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9749</v>
+        <v>-1.9499</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.3649</v>
       </c>
       <c r="S22" t="n">
-        <v>0.125</v>
+        <v>-0.5608</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3089</v>
+        <v>-0.9550999999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1839</v>
+        <v>0.3943</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.4535</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.2256</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.6791</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. MERLO</t>
+          <t>J. NWANKWO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2297,67 +2297,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.6315</v>
+        <v>-3.2666</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.8864</v>
+        <v>-3.526</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2549</v>
+        <v>0.2594</v>
       </c>
       <c r="G23" t="n">
-        <v>0.479</v>
+        <v>-1.6306</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.3263</v>
+        <v>-2.8132</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8053</v>
+        <v>1.1826</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.5425</v>
+        <v>-0.2219</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.664</v>
+        <v>-2.603</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1215</v>
+        <v>2.3811</v>
       </c>
       <c r="M23" t="n">
-        <v>1.0215</v>
+        <v>-1.4088</v>
       </c>
       <c r="N23" t="n">
-        <v>0.3377</v>
+        <v>-0.2102</v>
       </c>
       <c r="O23" t="n">
-        <v>0.6838</v>
+        <v>-1.1986</v>
       </c>
       <c r="P23" t="n">
-        <v>0.195</v>
+        <v>-1.5599</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9749</v>
+        <v>-2.9248</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1699</v>
+        <v>1.3649</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4754</v>
+        <v>0.2025</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.369</v>
+        <v>-0.3794</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1064</v>
+        <v>0.5818</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.8301</v>
+        <v>-0.2786</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.8301</v>
+        <v>-0.2786</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>L. BRYAN JR</t>
+          <t>S. IDRIS IGENE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2380,67 +2380,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.7129</v>
+        <v>-3.8418</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.4782</v>
+        <v>-3.4576</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.2347</v>
+        <v>-0.3842</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.5977</v>
+        <v>-1.4462</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.1156</v>
+        <v>-0.0593</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.4821</v>
+        <v>-1.3869</v>
       </c>
       <c r="J24" t="n">
-        <v>0.6261</v>
+        <v>-1.182</v>
       </c>
       <c r="K24" t="n">
-        <v>0.5046</v>
+        <v>0.082</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1215</v>
+        <v>-1.264</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.2238</v>
+        <v>-0.2642</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.6202</v>
+        <v>-0.1413</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.6036</v>
+        <v>-0.1229</v>
       </c>
       <c r="P24" t="n">
-        <v>0.195</v>
+        <v>-1.1699</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.9749</v>
+        <v>-1.9499</v>
       </c>
       <c r="R24" t="n">
-        <v>1.1699</v>
+        <v>0.7799</v>
       </c>
       <c r="S24" t="n">
-        <v>0.6475</v>
+        <v>-0.9472</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1294</v>
+        <v>-0.3258</v>
       </c>
       <c r="U24" t="n">
-        <v>0.7768</v>
+        <v>-0.6214</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.9577</v>
+        <v>-0.2786</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.9577</v>
+        <v>-0.2786</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>U. RAZAQUE</t>
+          <t>P. OSES BERNALDEZ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2463,67 +2463,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.9784</v>
+        <v>-8.887700000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.9102</v>
+        <v>-4.2974</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.0682</v>
+        <v>-4.5903</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.3791</v>
+        <v>-3.7162</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1116</v>
+        <v>-0.3155</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.4907</v>
+        <v>-3.4007</v>
       </c>
       <c r="J25" t="n">
-        <v>0.7692</v>
+        <v>-0.2068</v>
       </c>
       <c r="K25" t="n">
-        <v>1.2797</v>
+        <v>0.6441</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.5105</v>
+        <v>-0.851</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.1483</v>
+        <v>-3.5093</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.1681</v>
+        <v>-0.9596</v>
       </c>
       <c r="O25" t="n">
-        <v>0.0198</v>
+        <v>-2.5497</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.585</v>
+        <v>-3.3147</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.9499</v>
+        <v>-3.8997</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3649</v>
+        <v>0.585</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.5608</v>
+        <v>0.321</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.9550999999999999</v>
+        <v>-0.1909</v>
       </c>
       <c r="U25" t="n">
-        <v>0.3943</v>
+        <v>0.5118</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.4535</v>
+        <v>-2.1777</v>
       </c>
       <c r="W25" t="n">
-        <v>0.2256</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.6791</v>
+        <v>-2.1777</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>J. NWANKWO</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2546,318 +2546,69 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.2666</v>
+        <v>-16.179</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.526</v>
+        <v>-7.771399999999998</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2594</v>
+        <v>-8.407499999999999</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.6306</v>
+        <v>-3.3194</v>
       </c>
       <c r="H26" t="n">
-        <v>-2.8132</v>
+        <v>0.01700000000000035</v>
       </c>
       <c r="I26" t="n">
-        <v>1.1826</v>
+        <v>-3.3365</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.2219</v>
+        <v>9.136999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>-2.603</v>
+        <v>5.1856</v>
       </c>
       <c r="L26" t="n">
-        <v>2.3811</v>
+        <v>3.9512</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.4088</v>
+        <v>-12.4565</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.2102</v>
+        <v>-5.1683</v>
       </c>
       <c r="O26" t="n">
-        <v>-1.1986</v>
+        <v>-7.287899999999999</v>
       </c>
       <c r="P26" t="n">
-        <v>-1.5599</v>
+        <v>-6.824400000000001</v>
       </c>
       <c r="Q26" t="n">
-        <v>-2.9248</v>
+        <v>-16.5738</v>
       </c>
       <c r="R26" t="n">
-        <v>1.3649</v>
+        <v>9.749299999999998</v>
       </c>
       <c r="S26" t="n">
-        <v>0.2025</v>
+        <v>-0.4777</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.3794</v>
+        <v>-2.616</v>
       </c>
       <c r="U26" t="n">
-        <v>0.5818</v>
+        <v>2.1381</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.2786</v>
+        <v>-5.5572</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>2.2813</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.2786</v>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>play_by_play_2536116_LIGAREGULARA_PROCESSED.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>S. IDRIS IGENE</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>IREN BCBADAJOZ</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" t="n">
-        <v>-3.8418</v>
-      </c>
-      <c r="E27" t="n">
-        <v>-3.4576</v>
-      </c>
-      <c r="F27" t="n">
-        <v>-0.3842</v>
-      </c>
-      <c r="G27" t="n">
-        <v>-1.4462</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-0.0593</v>
-      </c>
-      <c r="I27" t="n">
-        <v>-1.3869</v>
-      </c>
-      <c r="J27" t="n">
-        <v>-1.182</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0.082</v>
-      </c>
-      <c r="L27" t="n">
-        <v>-1.264</v>
-      </c>
-      <c r="M27" t="n">
-        <v>-0.2642</v>
-      </c>
-      <c r="N27" t="n">
-        <v>-0.1413</v>
-      </c>
-      <c r="O27" t="n">
-        <v>-0.1229</v>
-      </c>
-      <c r="P27" t="n">
-        <v>-1.1699</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>-1.9499</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0.7799</v>
-      </c>
-      <c r="S27" t="n">
-        <v>-0.9472</v>
-      </c>
-      <c r="T27" t="n">
-        <v>-0.3258</v>
-      </c>
-      <c r="U27" t="n">
-        <v>-0.6214</v>
-      </c>
-      <c r="V27" t="n">
-        <v>-0.2786</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>-0.2786</v>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>play_by_play_2536116_LIGAREGULARA_PROCESSED.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>P. OSES BERNALDEZ</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>IREN BCBADAJOZ</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" t="n">
-        <v>-9.495200000000001</v>
-      </c>
-      <c r="E28" t="n">
-        <v>-4.905</v>
-      </c>
-      <c r="F28" t="n">
-        <v>-4.5903</v>
-      </c>
-      <c r="G28" t="n">
-        <v>-4.3237</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-0.3155</v>
-      </c>
-      <c r="I28" t="n">
-        <v>-4.0082</v>
-      </c>
-      <c r="J28" t="n">
-        <v>-0.8144</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0.6441</v>
-      </c>
-      <c r="L28" t="n">
-        <v>-1.4585</v>
-      </c>
-      <c r="M28" t="n">
-        <v>-3.5093</v>
-      </c>
-      <c r="N28" t="n">
-        <v>-0.9596</v>
-      </c>
-      <c r="O28" t="n">
-        <v>-2.5497</v>
-      </c>
-      <c r="P28" t="n">
-        <v>-3.3147</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>-3.8997</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0.585</v>
-      </c>
-      <c r="S28" t="n">
-        <v>0.321</v>
-      </c>
-      <c r="T28" t="n">
-        <v>-0.1909</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0.5118</v>
-      </c>
-      <c r="V28" t="n">
-        <v>-2.1777</v>
-      </c>
-      <c r="W28" t="n">
-        <v>0</v>
-      </c>
-      <c r="X28" t="n">
-        <v>-2.1777</v>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>play_by_play_2536116_LIGAREGULARA_PROCESSED.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>--- TOTAL ---</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>IREN BCBADAJOZ</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" t="n">
-        <v>-16.1791</v>
-      </c>
-      <c r="E29" t="n">
-        <v>-7.771599999999998</v>
-      </c>
-      <c r="F29" t="n">
-        <v>-8.407500000000001</v>
-      </c>
-      <c r="G29" t="n">
-        <v>-3.3195</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.01700000000000035</v>
-      </c>
-      <c r="I29" t="n">
-        <v>-3.3366</v>
-      </c>
-      <c r="J29" t="n">
-        <v>9.136799999999997</v>
-      </c>
-      <c r="K29" t="n">
-        <v>5.1856</v>
-      </c>
-      <c r="L29" t="n">
-        <v>3.9512</v>
-      </c>
-      <c r="M29" t="n">
-        <v>-12.4565</v>
-      </c>
-      <c r="N29" t="n">
-        <v>-5.1683</v>
-      </c>
-      <c r="O29" t="n">
-        <v>-7.2879</v>
-      </c>
-      <c r="P29" t="n">
-        <v>-6.824400000000001</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>-16.5738</v>
-      </c>
-      <c r="R29" t="n">
-        <v>9.749300000000002</v>
-      </c>
-      <c r="S29" t="n">
-        <v>-0.4777</v>
-      </c>
-      <c r="T29" t="n">
-        <v>-2.616</v>
-      </c>
-      <c r="U29" t="n">
-        <v>2.1381</v>
-      </c>
-      <c r="V29" t="n">
-        <v>-5.5572</v>
-      </c>
-      <c r="W29" t="n">
-        <v>2.2813</v>
-      </c>
-      <c r="X29" t="n">
-        <v>-7.8386</v>
-      </c>
-      <c r="Y29" t="inlineStr"/>
+        <v>-7.838600000000001</v>
+      </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
